--- a/Codes_2025/Trial 3/Trial3_Proposed (Gradient Boost)_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_Proposed (Gradient Boost)_Leaders_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
         <v>99.25285121909999</v>
       </c>
       <c r="F2" t="n">
-        <v>83.85135650634766</v>
+        <v>64.48516845703125</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,23 +504,23 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>52.34768683944106</v>
+        <v>52.64219647457018</v>
       </c>
       <c r="I2" t="n">
-        <v>17.18231316055901</v>
+        <v>16.8878035254299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>37.67999999999999</v>
+        <v>37.81</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50.54610131507693</v>
+        <v>37.22033627553438</v>
       </c>
       <c r="F3" t="n">
-        <v>36.60669708251953</v>
+        <v>49.73808670043945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>45.68423400400685</v>
+        <v>41.71736396815153</v>
       </c>
       <c r="I3" t="n">
-        <v>8.004234004006854</v>
+        <v>3.907363968151529</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>37.58000000000002</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25.1977926501113</v>
+        <v>50.54610131507693</v>
       </c>
       <c r="F4" t="n">
-        <v>54.79592514038086</v>
+        <v>42.53375625610352</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,23 +574,23 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>27.09426399303884</v>
+        <v>48.10680302642993</v>
       </c>
       <c r="I4" t="n">
-        <v>10.48573600696118</v>
+        <v>10.42680302642994</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>35.4</v>
+        <v>37.58000000000002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54.79771450242716</v>
+        <v>25.1977926501113</v>
       </c>
       <c r="F5" t="n">
-        <v>53.25020980834961</v>
+        <v>49.47833633422852</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,23 +609,23 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>52.34768683944106</v>
+        <v>27.71540443580511</v>
       </c>
       <c r="I5" t="n">
-        <v>16.94768683944106</v>
+        <v>9.864595564194914</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>22.34</v>
+        <v>35.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21.49547930685887</v>
+        <v>54.79771450242716</v>
       </c>
       <c r="F6" t="n">
-        <v>22.27248573303223</v>
+        <v>46.3512077331543</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -644,23 +644,23 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>21.02498933614366</v>
+        <v>52.64219647457018</v>
       </c>
       <c r="I6" t="n">
-        <v>1.315010663856338</v>
+        <v>17.24219647457018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>21.01</v>
+        <v>24.26000000000001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22.46325384117893</v>
+        <v>36.70529760187497</v>
       </c>
       <c r="F7" t="n">
-        <v>22.27452850341797</v>
+        <v>31.17228507995605</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -679,23 +679,23 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>21.94050358836786</v>
+        <v>37.06258313304592</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9305035883678627</v>
+        <v>12.80258313304591</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>20.08</v>
+        <v>22.34</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14.5973875851344</v>
+        <v>21.49547930685887</v>
       </c>
       <c r="F8" t="n">
-        <v>14.44857311248779</v>
+        <v>14.35878849029541</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>14.42477378972658</v>
+        <v>18.70090620630696</v>
       </c>
       <c r="I8" t="n">
-        <v>5.655226210273423</v>
+        <v>3.639093793693036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>10.19</v>
+        <v>21.01</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8.511111330196202</v>
+        <v>22.46325384117893</v>
       </c>
       <c r="F9" t="n">
-        <v>8.764396667480469</v>
+        <v>23.51420402526855</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -749,23 +749,23 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9.009826747488363</v>
+        <v>23.57690375314207</v>
       </c>
       <c r="I9" t="n">
-        <v>1.180173252511635</v>
+        <v>2.566903753142071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>9.359999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9.622454454199397</v>
+        <v>14.5973875851344</v>
       </c>
       <c r="F10" t="n">
-        <v>13.62217617034912</v>
+        <v>15.91829586029053</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -784,23 +784,23 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13.67985629814658</v>
+        <v>14.85955350901394</v>
       </c>
       <c r="I10" t="n">
-        <v>4.319856298146584</v>
+        <v>5.220446490986063</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.73</v>
+        <v>10.19</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.922944893692857</v>
+        <v>8.511111330196202</v>
       </c>
       <c r="F11" t="n">
-        <v>2.215464353561401</v>
+        <v>8.854074478149414</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -819,23 +819,23 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.83704655647997</v>
+        <v>10.04738097331222</v>
       </c>
       <c r="I11" t="n">
-        <v>4.89295344352003</v>
+        <v>0.1426190266877825</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>7.180000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.570951940213813</v>
+        <v>9.622454454199397</v>
       </c>
       <c r="F12" t="n">
-        <v>4.63149881362915</v>
+        <v>11.49831104278564</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -854,23 +854,23 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.041644178019932</v>
+        <v>11.31117155906534</v>
       </c>
       <c r="I12" t="n">
-        <v>2.138355821980069</v>
+        <v>1.951171559065346</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>6.590000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.058388586643492</v>
+        <v>1.922944893692857</v>
       </c>
       <c r="F13" t="n">
-        <v>6.377612113952637</v>
+        <v>2.440956354141235</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -889,45 +889,150 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.770192089173351</v>
+        <v>2.28572023353325</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1801920891733504</v>
+        <v>5.444279766466749</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7.180000000000001</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5.570951940213813</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.639776229858398</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5.09191724919014</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.08808275080986</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10.71820080519103</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.755702972412109</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10.04738097331222</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.237380973312216</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7.058388586643492</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8.657581329345703</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>8.776645530921469</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.186645530921468</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
         <v>6.549999999999999</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>6.9664063060335</v>
       </c>
-      <c r="F14" t="n">
-        <v>7.576059341430664</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Leaders</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>6.781856531434893</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.2318565314348939</v>
+      <c r="F17" t="n">
+        <v>7.586955070495605</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>6.788469009594196</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2384690095941968</v>
       </c>
     </row>
   </sheetData>
